--- a/site/Dayforce-Salesforce-Contacts-Sync-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Salesforce-Contacts-Sync-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -724,6 +724,28 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Correlation Settings</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KGM450J1YK3FN478G7X08MGN</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Contacts-Sync-Integration-Guide/#h_01KGM450J1YK3FN478G7X08MGN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Dayforce-Salesforce-Contacts-Sync-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Salesforce-Contacts-Sync-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,6 +746,226 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>User Lookup Configuration</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KJ52H23RGPH6Y4RD9H8JNQ6Y</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Contacts-Sync-Integration-Guide/#h_01KJ52H23RGPH6Y4RD9H8JNQ6Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Debug Settings</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Contacts-Sync-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Contacts-Sync-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Notification Settings</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Contacts-Sync-Integration-Guide/#h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Contacts-Sync-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Contacts-Sync-Integration-Guide/#h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Contacts-Sync-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KGHF9JDXCJXF0HYB7BRZ2P0E</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Contacts-Sync-Integration-Guide/#h_01KGHF9JDXCJXF0HYB7BRZ2P0E</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Log Insights</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Contacts-Sync-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Log Insight Settings</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KGHFA6Y71CG6DK6D0DZ6XTH1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Contacts-Sync-Integration-Guide/#h_01KGHFA6Y71CG6DK6D0DZ6XTH1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
